--- a/business_forms/036_gardening_supply_subscription_form--business_forms.xlsx
+++ b/business_forms/036_gardening_supply_subscription_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'weekly',_'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly', 'value': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'bi-weekly',_'value':_'bi-weekly'}</t>
+          <t>bi-weekly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Bi-Weekly', 'value': 'Bi-Weekly'}</t>
+          <t>Bi-Weekly</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'monthly',_'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly', 'value': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'spring',_'value':_'spring'}</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Spring', 'value': 'spring'}</t>
+          <t>Spring</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'summer',_'value':_'summer'}</t>
+          <t>summer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Summer', 'value': 'summer'}</t>
+          <t>Summer</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'fall',_'value':_'fall'}</t>
+          <t>fall</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Fall', 'value': 'fall'}</t>
+          <t>Fall</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'winter',_'value':_'winter'}</t>
+          <t>winter</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Winter', 'value': 'winter'}</t>
+          <t>Winter</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'once',_'value':_'once'}</t>
+          <t>once</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Once', 'value': 'once'}</t>
+          <t>Once</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'every_2_weeks',_'value':_'every_2_weeks'}</t>
+          <t>every_2_weeks</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Every 2 weeks', 'value': 'every 2 weeks'}</t>
+          <t>Every 2 weeks</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'every_4_weeks',_'value':_'every_4_weeks'}</t>
+          <t>every_4_weeks</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Every 4 weeks', 'value': 'every 4 weeks'}</t>
+          <t>Every 4 weeks</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'active',_'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Active', 'value': 'active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'inactive',_'value':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Inactive', 'value': 'inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'credit_card',_'value':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Credit Card', 'value': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'paypal',_'value':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'PayPal', 'value': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'every_2_weeks',_'value':_'every_2_weeks'}</t>
+          <t>every_2_weeks</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Every 2 weeks', 'value': 'every 2 weeks'}</t>
+          <t>Every 2 weeks</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'every_4_weeks',_'value':_'every_4_weeks'}</t>
+          <t>every_4_weeks</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Every 4 weeks', 'value': 'every 4 weeks'}</t>
+          <t>Every 4 weeks</t>
         </is>
       </c>
     </row>
